--- a/ventas/ventas_enero.xlsx
+++ b/ventas/ventas_enero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ac964b5a5586683/Documents/python_freelance_training/automatizacion-reportes-excel-python/ventas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{73F5A021-ECFC-4F2A-B034-07567E369B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96F80942-E902-4568-A75A-BE58DE6BC0E6}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{73F5A021-ECFC-4F2A-B034-07567E369B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DAF78B2-3EF3-4B0F-A092-AD18AD653EA6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" xr2:uid="{5CA83A14-5A0C-4589-8D72-4F72148E2D8C}"/>
+    <workbookView xWindow="1380" yWindow="2205" windowWidth="19800" windowHeight="10290" xr2:uid="{5CA83A14-5A0C-4589-8D72-4F72148E2D8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -47,28 +47,28 @@
     <t>cantidad</t>
   </si>
   <si>
+    <t>ciudad</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>San Juan</t>
+  </si>
+  <si>
+    <t>Ponce</t>
+  </si>
+  <si>
+    <t>Arecibo</t>
+  </si>
+  <si>
     <t>precio</t>
-  </si>
-  <si>
-    <t>ciudad</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>San Juan</t>
-  </si>
-  <si>
-    <t>Ponce</t>
-  </si>
-  <si>
-    <t>Arecibo</t>
   </si>
 </sst>
 </file>
@@ -121,6 +121,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -451,15 +455,15 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -468,12 +472,12 @@
         <v>800</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -482,12 +486,12 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -496,7 +500,7 @@
         <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
